--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6569.87</v>
+        <v>6485.28</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7934.05</v>
+        <v>8112.99</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1393-108-CM26</t>
+          <t>3706-315-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.140.300-9</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6485.28</v>
+        <v>1036.31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2724-465-CM26</t>
+          <t>1393-108-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,6 +630,67 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
+        <v>6485.28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2724-465-CM26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15.775.663-k</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>8112.99</v>
       </c>
     </row>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3706-315-CM25</t>
+          <t>1393-9-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.140.300-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1036.31</v>
+        <v>8585.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1393-108-CM26</t>
+          <t>1393-69-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6485.28</v>
+        <v>4654.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2724-465-CM26</t>
+          <t>2724-660-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,7 +691,678 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
+        <v>15800.29</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2724-724-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>16129.56</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2724-832-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>7669.89</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1393-204-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>7746.04</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3706-315-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.141.300-4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1036.31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1393-347-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>9487.530000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>229-808-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.141.100-1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FERMAT SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.814.662-2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>1734.96</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1052836-99-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>62.000.470-7</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PUNILLA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>COMERCIAL EL TORO SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.209.677-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>1580.31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1393-108-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>6485.28</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2724-465-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>15.775.663-k</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>8112.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1393-374-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.140.300-9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>6431.68</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2467-1005-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.292.846-7</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>3014.01</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1365,6 +1365,67 @@
         <v>3014.01</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>229-683-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.141.100-1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>FERMAT SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>77.814.662-2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>2120.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
@@ -623,7 +623,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>77.814.662-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1444,11 @@
           <t>77.814.662-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/nuble.xlsx
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
